--- a/companies/rusal/data/excel/rusal_unified.xlsx
+++ b/companies/rusal/data/excel/rusal_unified.xlsx
@@ -12260,6 +12260,9 @@
       <c r="P2" t="n">
         <v>849</v>
       </c>
+      <c r="Q2" t="n">
+        <v>537</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12314,6 +12317,9 @@
       <c r="P3" t="n">
         <v>6430</v>
       </c>
+      <c r="Q3" t="n">
+        <v>6858</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12368,6 +12374,9 @@
       <c r="P4" t="n">
         <v>754</v>
       </c>
+      <c r="Q4" t="n">
+        <v>1168</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12422,6 +12431,9 @@
       <c r="P5" t="n">
         <v>888</v>
       </c>
+      <c r="Q5" t="n">
+        <v>1204</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12476,6 +12488,9 @@
       <c r="P6" t="n">
         <v>15885</v>
       </c>
+      <c r="Q6" t="n">
+        <v>18453</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12530,6 +12545,9 @@
       <c r="P7" t="n">
         <v>586</v>
       </c>
+      <c r="Q7" t="n">
+        <v>753</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12584,6 +12602,9 @@
       <c r="P8" t="n">
         <v>753</v>
       </c>
+      <c r="Q8" t="n">
+        <v>982</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12638,6 +12659,9 @@
       <c r="P9" t="n">
         <v>2520</v>
       </c>
+      <c r="Q9" t="n">
+        <v>2652</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12692,6 +12716,9 @@
       <c r="P10" t="n">
         <v>3992</v>
       </c>
+      <c r="Q10" t="n">
+        <v>3918</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12746,6 +12773,9 @@
       <c r="P11" t="n">
         <v>9726</v>
       </c>
+      <c r="Q11" t="n">
+        <v>11909</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12799,6 +12829,9 @@
       </c>
       <c r="P12" t="n">
         <v>3859</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4490</v>
       </c>
     </row>
     <row r="13">
@@ -12998,6 +13031,9 @@
       <c r="P2" t="n">
         <v>849</v>
       </c>
+      <c r="Q2" t="n">
+        <v>537</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13052,6 +13088,9 @@
       <c r="P3" t="n">
         <v>6430</v>
       </c>
+      <c r="Q3" t="n">
+        <v>6858</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13106,6 +13145,9 @@
       <c r="P4" t="n">
         <v>754</v>
       </c>
+      <c r="Q4" t="n">
+        <v>1168</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13160,6 +13202,9 @@
       <c r="P5" t="n">
         <v>888</v>
       </c>
+      <c r="Q5" t="n">
+        <v>1204</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13214,6 +13259,9 @@
       <c r="P6" t="n">
         <v>15885</v>
       </c>
+      <c r="Q6" t="n">
+        <v>18453</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13268,6 +13316,9 @@
       <c r="P7" t="n">
         <v>586</v>
       </c>
+      <c r="Q7" t="n">
+        <v>753</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13322,6 +13373,9 @@
       <c r="P8" t="n">
         <v>753</v>
       </c>
+      <c r="Q8" t="n">
+        <v>982</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13376,6 +13430,9 @@
       <c r="P9" t="n">
         <v>2520</v>
       </c>
+      <c r="Q9" t="n">
+        <v>2652</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13430,6 +13487,9 @@
       <c r="P10" t="n">
         <v>3992</v>
       </c>
+      <c r="Q10" t="n">
+        <v>3918</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13484,6 +13544,9 @@
       <c r="P11" t="n">
         <v>9726</v>
       </c>
+      <c r="Q11" t="n">
+        <v>11909</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13537,6 +13600,9 @@
       </c>
       <c r="P12" t="n">
         <v>3859</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4490</v>
       </c>
     </row>
     <row r="13">
@@ -14784,7 +14850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14881,289 +14947,430 @@
       <c r="P2" t="n">
         <v>2520</v>
       </c>
+      <c r="Q2" t="n">
+        <v>2652</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>al_revenue_musd</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>9966</v>
-      </c>
-      <c r="N3" t="n">
-        <v>11593</v>
-      </c>
-      <c r="O3" t="n">
-        <v>10129</v>
-      </c>
-      <c r="P3" t="n">
-        <v>9726</v>
+          <t>al_production_kt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>kt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>3918</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>al_sales_kt</t>
+          <t>al_revenue_musd</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3904</v>
+        <v>9966</v>
       </c>
       <c r="N4" t="n">
-        <v>3896</v>
+        <v>11593</v>
       </c>
       <c r="O4" t="n">
-        <v>4153</v>
+        <v>10129</v>
       </c>
       <c r="P4" t="n">
-        <v>3859</v>
+        <v>9726</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>11909</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>alumina_avg_price_usd_t</t>
-        </is>
+          <t>al_sales_kt</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3904</v>
       </c>
       <c r="N5" t="n">
-        <v>470</v>
+        <v>3896</v>
       </c>
       <c r="O5" t="n">
-        <v>448</v>
+        <v>4153</v>
       </c>
       <c r="P5" t="n">
-        <v>510</v>
+        <v>3859</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4490</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>alumina_revenue_musd</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>533</v>
+          <t>alumina_avg_price_usd_t</t>
+        </is>
       </c>
       <c r="N6" t="n">
-        <v>550</v>
+        <v>470</v>
       </c>
       <c r="O6" t="n">
-        <v>340</v>
+        <v>448</v>
       </c>
       <c r="P6" t="n">
-        <v>453</v>
+        <v>510</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>537</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>alumina_sales_kt</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>1729</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1169</v>
-      </c>
-      <c r="O7" t="n">
-        <v>759</v>
-      </c>
-      <c r="P7" t="n">
-        <v>888</v>
+          <t>alumina_production_kt</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>kt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6858</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sales_geo_americas_musd</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>613</v>
-      </c>
-      <c r="H8" t="n">
-        <v>737</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1166</v>
-      </c>
-      <c r="K8" t="n">
-        <v>799</v>
+          <t>alumina_revenue_musd</t>
+        </is>
       </c>
       <c r="L8" t="n">
-        <v>624</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1087</v>
+        <v>533</v>
       </c>
       <c r="N8" t="n">
-        <v>1035</v>
+        <v>550</v>
       </c>
       <c r="O8" t="n">
-        <v>176</v>
+        <v>340</v>
       </c>
       <c r="P8" t="n">
-        <v>173</v>
+        <v>453</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sales_geo_asia_musd</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2110</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1723</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1939</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1381</v>
+          <t>alumina_sales_kt</t>
+        </is>
       </c>
       <c r="L9" t="n">
-        <v>1829</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2461</v>
+        <v>1729</v>
       </c>
       <c r="N9" t="n">
-        <v>3762</v>
+        <v>1169</v>
       </c>
       <c r="O9" t="n">
-        <v>4689</v>
+        <v>759</v>
       </c>
       <c r="P9" t="n">
-        <v>5189</v>
+        <v>888</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sales_geo_cis_musd</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>462</v>
-      </c>
-      <c r="H10" t="n">
-        <v>792</v>
-      </c>
-      <c r="I10" t="n">
-        <v>557</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2669</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2486</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3903</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4074</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3891</v>
-      </c>
-      <c r="P10" t="n">
-        <v>4107</v>
+          <t>bauxite_production_kt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>kt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>18453</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sales_geo_europe_musd</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>4698</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4394</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4753</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4805</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3574</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4401</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4989</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3397</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2554</v>
+          <t>electricity_usd_kwh</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>USD/kWh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sales_geo_other_musd</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>326</v>
-      </c>
-      <c r="H12" t="n">
-        <v>424</v>
-      </c>
-      <c r="K12" t="n">
-        <v>57</v>
-      </c>
-      <c r="L12" t="n">
-        <v>53</v>
-      </c>
-      <c r="M12" t="n">
-        <v>142</v>
-      </c>
-      <c r="N12" t="n">
-        <v>114</v>
-      </c>
-      <c r="O12" t="n">
-        <v>60</v>
-      </c>
-      <c r="P12" t="n">
-        <v>59</v>
+          <t>foil_other_revenue_musd</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MUSD</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>753</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>lme_al_avg_usd_t</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>other_products_revenue_musd</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MUSD</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sales_geo_americas_musd</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>613</v>
+      </c>
+      <c r="H15" t="n">
+        <v>737</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1166</v>
+      </c>
+      <c r="K15" t="n">
+        <v>799</v>
+      </c>
+      <c r="L15" t="n">
+        <v>624</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1087</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1035</v>
+      </c>
+      <c r="O15" t="n">
+        <v>176</v>
+      </c>
+      <c r="P15" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sales_geo_asia_musd</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2110</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1723</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1939</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1381</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1829</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2461</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3762</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4689</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5189</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>7671</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sales_geo_cis_musd</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>462</v>
+      </c>
+      <c r="H17" t="n">
+        <v>792</v>
+      </c>
+      <c r="I17" t="n">
+        <v>557</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2669</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2486</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3903</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4074</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3891</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4107</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4443</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sales_geo_europe_musd</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>4698</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4394</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4753</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4805</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3574</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4401</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4989</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3397</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2554</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sales_geo_other_musd</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>326</v>
+      </c>
+      <c r="H19" t="n">
+        <v>424</v>
+      </c>
+      <c r="K19" t="n">
+        <v>57</v>
+      </c>
+      <c r="L19" t="n">
+        <v>53</v>
+      </c>
+      <c r="M19" t="n">
+        <v>142</v>
+      </c>
+      <c r="N19" t="n">
+        <v>114</v>
+      </c>
+      <c r="O19" t="n">
+        <v>60</v>
+      </c>
+      <c r="P19" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>sales_geo_total_musd</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K20" t="n">
         <v>9711</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L20" t="n">
         <v>8566</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M20" t="n">
         <v>11994</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N20" t="n">
         <v>13974</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O20" t="n">
         <v>12213</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P20" t="n">
         <v>12082</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>14812</v>
       </c>
     </row>
   </sheetData>
@@ -15290,7 +15497,7 @@
         <v>26</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>26.56</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15332,7 +15539,7 @@
         <v>26</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>26.56</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16024,6 +16231,9 @@
       <c r="O16" s="4" t="n">
         <v>-44</v>
       </c>
+      <c r="P16" s="4" t="n">
+        <v>-30</v>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>mUSD</t>
@@ -16329,6 +16539,9 @@
       </c>
       <c r="O22" s="4" t="n">
         <v>-286</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>-211</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -20125,7 +20338,7 @@
         <v>-127</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>151</v>
+        <v>-99</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -20341,7 +20554,7 @@
         <v>-65</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-65</v>
+        <v>102</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
